--- a/diseases/d140/2015-2019.xlsx
+++ b/diseases/d140/2015-2019.xlsx
@@ -35400,9 +35400,6 @@
       <c r="P236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -35950,9 +35947,6 @@
       <c r="P239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -36500,9 +36494,6 @@
       <c r="P242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -37050,9 +37041,6 @@
       <c r="P245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -37600,9 +37588,6 @@
       <c r="P248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -38150,9 +38135,6 @@
       <c r="P251" t="n">
         <v>1</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -38700,9 +38682,6 @@
       <c r="P254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -39250,9 +39229,6 @@
       <c r="P257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -39800,9 +39776,6 @@
       <c r="P260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -40350,9 +40323,6 @@
       <c r="P263" t="n">
         <v>1</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -40900,9 +40870,6 @@
       <c r="P266" t="n">
         <v>1</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -41450,9 +41417,6 @@
       <c r="P269" t="n">
         <v>2</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.5544781736597916</v>
       </c>
@@ -42000,9 +41964,6 @@
       <c r="P272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -42550,9 +42511,6 @@
       <c r="P275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -43100,9 +43058,6 @@
       <c r="P278" t="n">
         <v>3</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.8317172604896874</v>
       </c>
@@ -43650,9 +43605,6 @@
       <c r="P281" t="n">
         <v>2</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.5544781736597916</v>
       </c>
@@ -44200,9 +44152,6 @@
       <c r="P284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -44750,9 +44699,6 @@
       <c r="P287" t="n">
         <v>1</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -45300,9 +45246,6 @@
       <c r="P290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -45850,9 +45793,6 @@
       <c r="P293" t="n">
         <v>1</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -46400,9 +46340,6 @@
       <c r="P296" t="n">
         <v>2</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.5544781736597916</v>
       </c>
@@ -46950,9 +46887,6 @@
       <c r="P299" t="n">
         <v>2</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.5544781736597916</v>
       </c>
@@ -47500,9 +47434,6 @@
       <c r="P302" t="n">
         <v>4</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>1.108956347319583</v>
       </c>
@@ -48050,9 +47981,6 @@
       <c r="P305" t="n">
         <v>1</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.2772390868298958</v>
       </c>
@@ -48600,9 +48528,6 @@
       <c r="P308" t="n">
         <v>2</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.5544781736597916</v>
       </c>
@@ -49150,9 +49075,6 @@
       <c r="P311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -49699,9 +49621,6 @@
       </c>
       <c r="P314" t="n">
         <v>2</v>
-      </c>
-      <c r="Q314" t="n">
-        <v>0</v>
       </c>
       <c r="R314" t="n">
         <v>0.5544781736597916</v>
